--- a/Milch2.xlsx
+++ b/Milch2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="263">
   <si>
     <t>Name</t>
   </si>
@@ -408,6 +408,12 @@
     <t>Glukosesirup, Kokosfett, Hafermehl 20%, hydrolisiertes Erbsenprotein, Stabilisator (E340ii), Trennmittel (E341iii), Emulgator ( E472e)</t>
   </si>
   <si>
+    <t>High Calcium Soy Milk Powder Yon Ho</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
     <t>Malz</t>
   </si>
   <si>
@@ -543,7 +549,7 @@
     <t>Bitter Nachgeschmack</t>
   </si>
   <si>
-    <t>Säureregulator Natriumhydrogencarbonat, Säureregulator Natriumcitrate, Süßungsmittel Steviolglycoside aus Stevia (21 %), Trennmittel L – Leucin.</t>
+    <t>Säureregulator Natriumhydrogencarbonat, Säureregulator Natriumcitrate, Süßungsmittel Steviolglycoside aus Stevia (21 %), Trennmittel L–Leucin.</t>
   </si>
   <si>
     <t>Bulk Supplements Aspartam</t>
@@ -558,7 +564,7 @@
     <t>Leber Krebs, Diabetes, Herz-Kreislauf-Erkrankungen , Schlaganfälle</t>
   </si>
   <si>
-    <t>Beliebten Süssstoff, er so "natürlich" nach Zucker schmeckt</t>
+    <t>Beliebten Süssstoff, er so "natürlich" nach Zucker schmeckt.</t>
   </si>
   <si>
     <t>Borchers Sucralose Tabletten</t>
@@ -567,13 +573,13 @@
     <t>DNA-Schädigungen, Blutzuckerspiegel</t>
   </si>
   <si>
-    <t>Dextrose, Süßungsmittel: 12 % Sucralose (E 955), vernetzte Carboxymethylcellulose E 468, Vanillearoma</t>
+    <t>Dextrose, Süßungsmittel: 12 % Sucralose (E 955), vernetzte Carboxymethylcellulose E 468, Vanillearoma.</t>
   </si>
   <si>
     <t>Borchers Sucralose Pulver</t>
   </si>
   <si>
-    <t>Maltodextrin, Sucralose</t>
+    <t>Maltodextrin, Sucralose.</t>
   </si>
   <si>
     <t>Jeden Tag Tabletten Saccharin</t>
@@ -582,28 +588,28 @@
     <t>Verstopfung</t>
   </si>
   <si>
-    <t>Süßungsmittel: 66,7% Cyclamat; Säureregulatoren: Natriumcarbonate, Weinsäure (L+); Süßungsmittel: 6,7% Saccharin</t>
+    <t>Süßungsmittel: 66,7% Cyclamat; Säureregulatoren: Natriumcarbonate, Weinsäure (L+); Süßungsmittel: 6,7% Saccharin.</t>
   </si>
   <si>
     <t>Süsstoff Kandisin Classic Tabletten Saccharin</t>
   </si>
   <si>
-    <t>Süßungsmittel Natrium-Cyclamat (E952), Füllstoff Natriumhydrogencarbonat (E500), Süßungsmittel Natrium-Saccharin (E954), Säuerungsmittel Weinsäure (E334)</t>
-  </si>
-  <si>
-    <t>Saporepuro Maltitol Pulver ( Maltit )</t>
+    <t>Süßungsmittel Natrium-Cyclamat (E952), Füllstoff Natriumhydrogencarbonat (E500), Süßungsmittel Natrium-Saccharin (E954), Säuerungsmittel Weinsäure (E334).</t>
+  </si>
+  <si>
+    <t>Saporepuro Maltitol Pulver, Maltit</t>
   </si>
   <si>
     <t>Durchfall, Einfluss auf den Blutzuckerspiegel</t>
   </si>
   <si>
-    <t>100% MALITIT ( Maltitol E965i )</t>
+    <t>100% MALITIT, Maltitol E965i.</t>
   </si>
   <si>
     <t>Saporepuro SORBIT Pulver</t>
   </si>
   <si>
-    <t>Pflanzlich aus Mais oder Kartoffeln</t>
+    <t>Pflanzlich aus Mais oder Kartoffeln.</t>
   </si>
   <si>
     <t>Saporepuro Erythrit Pulver</t>
@@ -612,25 +618,25 @@
     <t>Durchfall, Herzschlag</t>
   </si>
   <si>
-    <t>Kalorienfreier, natürlicher Zuckeraustauschstoff aus der Gruppe der Zuckeralkohole, der zu ca. 70 % die Süßkraft von Zucker besitzt. Er wird meist durch Fermentation von Mais gewonnen, schmeckt ähnlich wie Zucker und ist ideal für Diabetiker oder eine Low-Carb-Ernährung, da er den Blutzucker nicht beeinflusst</t>
+    <t>Kalorienfreier, natürlicher Zuckeraustauschstoff aus der Gruppe der Zuckeralkohole, der zu ca. 70 % die Süßkraft von Zucker besitzt. Er wird meist durch Fermentation von Mais gewonnen, schmeckt ähnlich wie Zucker und ist ideal für Diabetiker oder eine Low-Carb-Ernährung, da er den Blutzucker nicht beeinflusst.</t>
   </si>
   <si>
     <t>Saporepuro Xylit Pulver</t>
   </si>
   <si>
-    <t>Xylit ursprünglich aus der Rinde von Birken gewonnen wurde</t>
-  </si>
-  <si>
-    <t>Alnatura Bio Rübenzucker (Saccharose)</t>
+    <t>Xylit ursprünglich aus der Rinde von Birken gewonnen wurde.</t>
+  </si>
+  <si>
+    <t>Alnatura Bio Rübenzucker, Saccharose</t>
   </si>
   <si>
     <t>Saccharose (Haushaltszucker) liefert viele Kalorien ohne Nährstoffe, lässt den Blutzuckerspiegel schnell ansteigen und fördert bei übermäßigem Konsum KariesÜbergewicht sowie das Risiko für Typ-2-Diabetes, Herz-Kreislauf-Erkrankungen und Fettleber.</t>
   </si>
   <si>
-    <t>Aus Saccharose besteht</t>
-  </si>
-  <si>
-    <t>Sweet Family Fruktose (Fruchtzucker)</t>
+    <t>Aus Saccharose besteht.</t>
+  </si>
+  <si>
+    <t>Sweet Family Fruktose, Fruchtzucker</t>
   </si>
   <si>
     <t>Einfluss auf den Blutzuckerspiegel, Fördert Diabetes, Gewicht zunahme, schlechte Stoffwechsel. Schlechteste Zucker, in Leber in Fett umgewandelt.</t>
@@ -648,13 +654,13 @@
     <t>Aus Laktose.</t>
   </si>
   <si>
-    <t>Mivolis Traubenzucker ( Dextrose, Glukose )</t>
+    <t>Mivolis Traubenzucker, Dextrose, Glukose</t>
   </si>
   <si>
     <t>Zahnkaries, Durchfall, Blutzucker-Achterbahn &amp; Heißhunger</t>
   </si>
   <si>
-    <t>Zutaten: Traubenzucker (91%), Ascorbinsäure (Vitamin C), Nicotinamid, DL-alpha-Tocopherylacetat (Vitamin E), Calcium-D-pantothenat, Pyridoxinhydrochlorid (Vitamin B6), Riboflavin (Vitamin B2), Thiaminmononitrat (Vitamin B1),Pteroylmonoglutaminsäure (Folsäure), D-Biotin, Cyanocobalamin (Vitamin B12).</t>
+    <t>Zutaten: Traubenzucker (91%), Ascorbinsäure (Vitamin C), Nicotinamid, DL-alpha-Tocopherylacetat (Vitamin E), Calcium-D-pantothenat, Pyridoxinhydrochlorid (Vitamin B6), Riboflavin (Vitamin B2), Thiaminmononitrat.(Vitamin)B1),Pteroylmonoglutaminsäure (Folsäure), D-Biotin, Cyanocobalamin (Vitamin B12).</t>
   </si>
   <si>
     <t>Bad Leonhard Maiszucker</t>
@@ -663,16 +669,16 @@
     <t>Fettleber &amp; Stoffwechselerkrankungen, fördert übergewicht</t>
   </si>
   <si>
-    <t>Fructosefreie, vegane Alternative zu Haushaltszucker, die aus Maisstärke gewonnen</t>
-  </si>
-  <si>
-    <t>Grafschafter Goldsaft Zuckerrübensirup (Golden Sirup )</t>
+    <t>Fructosefreie, vegane Alternative zu Haushaltszucker, die aus Maisstärke gewonnen.</t>
+  </si>
+  <si>
+    <t>Grafschafter Goldsaft Zuckerrübensirup, Golden Sirup</t>
   </si>
   <si>
     <t>Sehr hoher Zuckergehalt, nicht für diabetiker</t>
   </si>
   <si>
-    <t>Ein naturreiner Zuckerrübensirup. Der Rübensaft wird durch das Abpressen von gekochten Rübenschnitzeln gewonnen</t>
+    <t>Ein naturreiner Zuckerrübensirup. Der Rübensaft wird durch das Abpressen von gekochten Rübenschnitzeln gewonnen.</t>
   </si>
   <si>
     <t>Langnese Flotte Biene Wildblütenhonig</t>
@@ -681,7 +687,7 @@
     <t>fördert Karies und kann den Blutzuckerspiegel stark erhöhen, Antibiotika, Pestiziden</t>
   </si>
   <si>
-    <t>Aus dem Nektar verschiedener Wild- und Wiesenblumen</t>
+    <t>Aus dem Nektar verschiedener Wild- und Wiesenblumen.</t>
   </si>
   <si>
     <t>Ahornsirup Grad A DM Drogerie</t>
@@ -693,7 +699,7 @@
     <t>Blutzucker schnell ansteigen lässt, nicht stark</t>
   </si>
   <si>
-    <t>Eingekochter Saft des kanadischen Zuckerahorns, natürliches veganes Süßungsmittel</t>
+    <t>Eingekochter Saft des kanadischen Zuckerahorns, natürliches veganes Süßungsmittel.</t>
   </si>
   <si>
     <t>Yacon Sirup AcanChia Rohkostqualität</t>
@@ -705,7 +711,7 @@
     <t>Ideal für Diabetiker, aus Yacon Wurzel.</t>
   </si>
   <si>
-    <t>Luo Han Guo VitaSanum - Mönchsfrucht Pulver</t>
+    <t>Luo Han Guo VitaSanum, Mönchsfrucht Pulver</t>
   </si>
   <si>
     <t>Herz-Kreislauf-Erkrankungen wie Schlaganfälle und Herzinfarkte</t>
@@ -714,7 +720,7 @@
     <t>Eine kleine, grüne Frucht aus Südchina.</t>
   </si>
   <si>
-    <t>Rapunzel Zuckerrohr Melasse (Maltose, Malz Zucker )</t>
+    <t>Rapunzel Zuckerrohr Melasse, Maltose, Malz Zucker</t>
   </si>
   <si>
     <t>Fördert Übergewicht, schadet dem Zahnschmelz</t>
@@ -738,7 +744,7 @@
     <t>Durchfall, negativ Darmmikrobiom, Krebs, Blutzuckerspiegel sowie Stoffwechselprozesse zu beeinflussen, Aftertaste</t>
   </si>
   <si>
-    <t>Der Süßstoff ist das Kaliumsalz des Acesulfams, das Acesulfam-Kalium oder Acesulfam</t>
+    <t>Der Süßstoff ist das Kaliumsalz des Acesulfams, das Acesulfam-Kalium oder Acesulfam.</t>
   </si>
   <si>
     <t>Damhert Tagatesse Dispenser</t>
@@ -756,7 +762,7 @@
     <t>Blähung, wenig süss</t>
   </si>
   <si>
-    <t>Oligofruktose, Fruktose, Glukose und Saccharose in Wasser</t>
+    <t>Oligofruktose, Fruktose, Glukose und Saccharose in Wasser.</t>
   </si>
   <si>
     <t>Bulk Supplements Mannitol Powder</t>
@@ -768,7 +774,7 @@
     <t>Durchfall, Reizdarmsyndrom, stark entwässernd wirkt</t>
   </si>
   <si>
-    <t>6-wertiger Zuckeralkohol, der als stark osmotisch wirkendes Diuretikum zur Behandlung von Hirnödemen, zur Steigerung der Harnausscheidung (akutes Nierenversagen) und als Süßungsmittel verwendet wird</t>
+    <t>6-wertiger Zuckeralkohol, der als stark osmotisch wirkendes Diuretikum zur Behandlung von Hirnödemen, zur Steigerung der Harnausscheidung (akutes Nierenversagen) und als Süßungsmittel verwendet wird.</t>
   </si>
   <si>
     <t>Lorann Isomalt</t>
@@ -792,10 +798,10 @@
     <t>Saporepuro Glukosesirup</t>
   </si>
   <si>
-    <t>Hohes Diabetes Risiko, Kein Nährwert, Förderung von Übergewicht, Fett und Stoffwechselstörungen, Blutzuckerspiegel Schwankungen, Karies.</t>
-  </si>
-  <si>
-    <t>Billig Dextrose-Äquivalent. Dicker, transparenter, farbloser Sirup. Es senkt den Gefrierpunkt und ist ideal ür Gebäck und Eis.</t>
+    <t>Hohes Diabetes Risiko, Kein Nährwert, Förderung von Übergewicht, Fett und Stoffwechselstörungen, Blutzuckerspiegel Schwankungen, Karies</t>
+  </si>
+  <si>
+    <t>Billig Dextrose Äquivalent. Dicker, transparenter, farbloser Sirup. Es senkt den Gefrierpunkt und ist ideal ür Gebäck und Eis.</t>
   </si>
 </sst>
 </file>
@@ -1164,14 +1170,14 @@
         <v>35.0</v>
       </c>
       <c r="K2" s="2">
-        <f t="shared" ref="K2:K55" si="1">J2/I2</f>
+        <f t="shared" ref="K2:K56" si="1">J2/I2</f>
         <v>35</v>
       </c>
       <c r="L2" s="1">
         <v>55.0</v>
       </c>
       <c r="M2" s="2">
-        <f t="shared" ref="M2:M44" si="2">L2/H2</f>
+        <f t="shared" ref="M2:M45" si="2">L2/H2</f>
         <v>1</v>
       </c>
       <c r="N2" s="1">
@@ -3278,7 +3284,7 @@
         <v>1.9</v>
       </c>
       <c r="M45" s="2">
-        <f t="shared" ref="M45:M55" si="3">L45/$H$45</f>
+        <f t="shared" si="2"/>
         <v>0.7037037037</v>
       </c>
       <c r="N45" s="1">
@@ -3327,8 +3333,7 @@
         <v>0.0</v>
       </c>
       <c r="M46" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N46" s="1">
         <v>0.1</v>
@@ -3376,8 +3381,7 @@
         <v>0.0</v>
       </c>
       <c r="M47" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N47" s="1">
         <v>0.1</v>
@@ -3425,7 +3429,7 @@
         <v>0.0</v>
       </c>
       <c r="M48" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="M48:M56" si="3">L48/H48</f>
         <v>0</v>
       </c>
       <c r="N48" s="1">
@@ -3475,7 +3479,7 @@
       </c>
       <c r="M49" s="2">
         <f t="shared" si="3"/>
-        <v>0.1851851852</v>
+        <v>0.4166666667</v>
       </c>
       <c r="N49" s="1">
         <v>0.12</v>
@@ -3524,7 +3528,7 @@
       </c>
       <c r="M50" s="2">
         <f t="shared" si="3"/>
-        <v>1.814814815</v>
+        <v>1</v>
       </c>
       <c r="N50" s="1">
         <v>0.13</v>
@@ -3573,7 +3577,7 @@
       </c>
       <c r="M51" s="2">
         <f t="shared" si="3"/>
-        <v>1.814814815</v>
+        <v>1</v>
       </c>
       <c r="N51" s="1">
         <v>0.13</v>
@@ -3622,7 +3626,7 @@
       </c>
       <c r="M52" s="2">
         <f t="shared" si="3"/>
-        <v>1.777777778</v>
+        <v>1</v>
       </c>
       <c r="N52" s="1">
         <v>0.13</v>
@@ -3671,7 +3675,7 @@
       </c>
       <c r="M53" s="2">
         <f t="shared" si="3"/>
-        <v>1.888888889</v>
+        <v>1</v>
       </c>
       <c r="N53" s="1">
         <v>0.13</v>
@@ -3720,7 +3724,7 @@
       </c>
       <c r="M54" s="2">
         <f t="shared" si="3"/>
-        <v>4.074074074</v>
+        <v>0.1506849315</v>
       </c>
       <c r="N54" s="1">
         <v>0.06</v>
@@ -3769,7 +3773,7 @@
       </c>
       <c r="M55" s="2">
         <f t="shared" si="3"/>
-        <v>2.814814815</v>
+        <v>0.1206349206</v>
       </c>
       <c r="N55" s="1">
         <v>0.51</v>
@@ -3779,13 +3783,58 @@
       </c>
     </row>
     <row r="56">
-      <c r="M56" s="3"/>
+      <c r="A56" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="1">
+        <v>461.0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="K56" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M56" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="57">
-      <c r="M57" s="3"/>
+      <c r="K57" s="2"/>
+      <c r="M57" s="2"/>
     </row>
     <row r="58">
-      <c r="M58" s="3"/>
+      <c r="K58" s="2"/>
+      <c r="M58" s="2"/>
     </row>
     <row r="59">
       <c r="M59" s="3"/>
@@ -6620,7 +6669,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>8</v>
@@ -6640,7 +6689,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
@@ -6672,7 +6721,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
@@ -6704,7 +6753,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>37</v>
@@ -6736,7 +6785,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>64</v>
@@ -6768,7 +6817,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>16</v>
@@ -6800,7 +6849,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>37</v>
@@ -6832,7 +6881,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>16</v>
@@ -6864,7 +6913,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>37</v>
@@ -6896,7 +6945,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>27</v>
@@ -6928,7 +6977,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>16</v>
@@ -6960,7 +7009,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>25</v>
@@ -6992,10 +7041,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -7024,7 +7073,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>16</v>
@@ -7056,7 +7105,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>16</v>
@@ -7088,7 +7137,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
@@ -7120,7 +7169,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
@@ -7152,7 +7201,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
@@ -7184,7 +7233,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
@@ -7216,7 +7265,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>64</v>
@@ -7248,7 +7297,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>16</v>
@@ -7280,7 +7329,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
@@ -7312,7 +7361,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
@@ -7344,7 +7393,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>16</v>
@@ -7376,7 +7425,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>37</v>
@@ -7408,7 +7457,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>16</v>
@@ -7440,7 +7489,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>25</v>
@@ -7472,7 +7521,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
@@ -7501,7 +7550,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>18</v>
@@ -7530,7 +7579,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>18</v>
@@ -7559,10 +7608,10 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>18</v>
@@ -7591,7 +7640,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>16</v>
@@ -7653,37 +7702,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>14</v>
@@ -7691,7 +7740,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B2" s="1">
         <v>0.0</v>
@@ -7715,24 +7764,24 @@
         <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J2" s="4">
         <v>0.0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B3" s="1">
         <v>0.0</v>
@@ -7756,24 +7805,24 @@
         <v>56</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J3" s="4">
         <v>0.0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B4" s="1">
         <v>0.0</v>
@@ -7797,24 +7846,24 @@
         <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J4" s="4">
         <v>0.0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B5" s="1">
         <v>0.0</v>
@@ -7838,24 +7887,24 @@
         <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J5" s="4">
         <v>0.0</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B6" s="1">
         <v>0.0</v>
@@ -7879,24 +7928,24 @@
         <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J6" s="4">
         <v>0.9</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B7" s="1">
         <v>0.0</v>
@@ -7920,24 +7969,24 @@
         <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J7" s="4">
         <v>0.9</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B8" s="1">
         <v>210.0</v>
@@ -7961,24 +8010,24 @@
         <v>53</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J8" s="4">
         <v>1.0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B9" s="1">
         <v>260.0</v>
@@ -8002,24 +8051,24 @@
         <v>104</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J9" s="4">
         <v>1.0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B10" s="1">
         <v>0.0</v>
@@ -8043,24 +8092,24 @@
         <v>104</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J10" s="4">
         <v>0.0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B11" s="1">
         <v>240.0</v>
@@ -8084,24 +8133,24 @@
         <v>104</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J11" s="4">
         <v>1.0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B12" s="1">
         <v>387.0</v>
@@ -8125,24 +8174,24 @@
         <v>16</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J12" s="4">
         <v>1.0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B13" s="1">
         <v>400.0</v>
@@ -8166,24 +8215,24 @@
         <v>16</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J13" s="4">
         <v>0.99</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B14" s="1">
         <v>380.0</v>
@@ -8207,24 +8256,24 @@
         <v>16</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J14" s="4">
         <v>0.95</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B15" s="1">
         <v>364.0</v>
@@ -8248,24 +8297,24 @@
         <v>16</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J15" s="4">
         <v>0.91</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B16" s="1">
         <v>396.0</v>
@@ -8289,24 +8338,24 @@
         <v>25</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J16" s="4">
         <v>0.99</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B17" s="1">
         <v>306.0</v>
@@ -8330,24 +8379,24 @@
         <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J17" s="4">
         <v>0.69</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B18" s="1">
         <v>302.0</v>
@@ -8371,24 +8420,24 @@
         <v>16</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J18" s="4">
         <v>0.75</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B19" s="1">
         <v>356.0</v>
@@ -8409,27 +8458,27 @@
         <v>54.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J19" s="4">
         <v>0.89</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B20" s="1">
         <v>197.0</v>
@@ -8453,24 +8502,24 @@
         <v>16</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J20" s="4">
         <v>0.36</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B21" s="1">
         <v>0.0</v>
@@ -8494,24 +8543,24 @@
         <v>16</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J21" s="4">
         <v>0.97</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B22" s="1">
         <v>297.0</v>
@@ -8535,24 +8584,24 @@
         <v>16</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J22" s="4">
         <v>0.7</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B23" s="1">
         <v>300.0</v>
@@ -8576,24 +8625,24 @@
         <v>16</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J23" s="4">
         <v>0.75</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B24" s="1">
         <v>0.0</v>
@@ -8617,24 +8666,24 @@
         <v>16</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J24" s="4">
         <v>0.0</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B25" s="1">
         <v>160.0</v>
@@ -8658,24 +8707,24 @@
         <v>101</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J25" s="4">
         <v>0.78</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B26" s="1">
         <v>168.0</v>
@@ -8699,24 +8748,24 @@
         <v>67</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J26" s="4">
         <v>0.1</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B27" s="1">
         <v>160.0</v>
@@ -8737,27 +8786,27 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J27" s="4">
         <v>0.99</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B28" s="1">
         <v>240.0</v>
@@ -8778,27 +8827,27 @@
         <v>9.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J28" s="4">
         <v>0.99</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B29" s="1">
         <v>0.0</v>
@@ -8822,24 +8871,24 @@
         <v>37</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J29" s="4">
         <v>0.1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B30" s="1">
         <v>324.0</v>
@@ -8860,19 +8909,19 @@
         <v>104</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J30" s="4">
         <v>0.81</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
